--- a/artfynd/A 39659-2024 artfynd.xlsx
+++ b/artfynd/A 39659-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131038697</v>
+        <v>135173948</v>
       </c>
       <c r="B2" t="n">
-        <v>97986</v>
+        <v>109896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>220204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,17 +703,33 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Karlslund, Vg</t>
+          <t>Slätte, N, vid järnvägsviadukten, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455207</v>
+        <v>454926</v>
       </c>
       <c r="R2" t="n">
-        <v>6515782</v>
+        <v>6515659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,25 +770,26 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131038700</v>
+        <v>131038697</v>
       </c>
       <c r="B3" t="n">
         <v>97986</v>
@@ -807,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455161</v>
+        <v>455207</v>
       </c>
       <c r="R3" t="n">
-        <v>6515762</v>
+        <v>6515782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +886,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131038701</v>
+        <v>131038700</v>
       </c>
       <c r="B4" t="n">
         <v>97986</v>
@@ -904,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455110</v>
+        <v>455161</v>
       </c>
       <c r="R4" t="n">
-        <v>6515741</v>
+        <v>6515762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131038703</v>
+        <v>131038701</v>
       </c>
       <c r="B5" t="n">
         <v>97986</v>
@@ -1001,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454998</v>
+        <v>455110</v>
       </c>
       <c r="R5" t="n">
-        <v>6515703</v>
+        <v>6515741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1077,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131038703</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Karlslund, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>454998</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6515703</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Töreboda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älgarås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39659-2024 artfynd.xlsx
+++ b/artfynd/A 39659-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135173948</v>
+        <v>131038697</v>
       </c>
       <c r="B2" t="n">
-        <v>109896</v>
+        <v>97986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,33 +703,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slätte, N, vid järnvägsviadukten, Vg</t>
+          <t>Karlslund, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454926</v>
+        <v>455207</v>
       </c>
       <c r="R2" t="n">
-        <v>6515659</v>
+        <v>6515782</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,26 +754,25 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Anna Sjövall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Anna Sjövall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131038697</v>
+        <v>131038700</v>
       </c>
       <c r="B3" t="n">
         <v>97986</v>
@@ -824,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455207</v>
+        <v>455161</v>
       </c>
       <c r="R3" t="n">
-        <v>6515782</v>
+        <v>6515762</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131038700</v>
+        <v>131038701</v>
       </c>
       <c r="B4" t="n">
         <v>97986</v>
@@ -921,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455161</v>
+        <v>455110</v>
       </c>
       <c r="R4" t="n">
-        <v>6515762</v>
+        <v>6515741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131038701</v>
+        <v>131038703</v>
       </c>
       <c r="B5" t="n">
         <v>97986</v>
@@ -1018,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455110</v>
+        <v>454998</v>
       </c>
       <c r="R5" t="n">
-        <v>6515741</v>
+        <v>6515703</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,103 +1060,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>131038703</v>
-      </c>
-      <c r="B6" t="n">
-        <v>97986</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>221946</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Karlslund, Vg</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>454998</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6515703</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Töreboda</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Älgarås</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39659-2024 artfynd.xlsx
+++ b/artfynd/A 39659-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,27 +680,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131038697</v>
+        <v>135173948</v>
       </c>
       <c r="B2" t="n">
-        <v>97986</v>
+        <v>109984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>220204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,17 +708,33 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Karlslund, Vg</t>
+          <t>Slätte, N, vid järnvägsviadukten, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455207</v>
+        <v>454926</v>
       </c>
       <c r="R2" t="n">
-        <v>6515782</v>
+        <v>6515659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,30 +775,31 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Sjövall</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131038697</t>
+          <t>https://artportalen.se/Sighting/135173948</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131038700</v>
+        <v>131038697</v>
       </c>
       <c r="B3" t="n">
         <v>97986</v>
@@ -817,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455161</v>
+        <v>455207</v>
       </c>
       <c r="R3" t="n">
-        <v>6515762</v>
+        <v>6515782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,13 +895,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131038700</t>
+          <t>https://artportalen.se/Sighting/131038697</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131038701</v>
+        <v>131038700</v>
       </c>
       <c r="B4" t="n">
         <v>97986</v>
@@ -919,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455110</v>
+        <v>455161</v>
       </c>
       <c r="R4" t="n">
-        <v>6515741</v>
+        <v>6515762</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,13 +997,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131038701</t>
+          <t>https://artportalen.se/Sighting/131038700</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131038703</v>
+        <v>131038701</v>
       </c>
       <c r="B5" t="n">
         <v>97986</v>
@@ -1021,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454998</v>
+        <v>455110</v>
       </c>
       <c r="R5" t="n">
-        <v>6515703</v>
+        <v>6515741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,6 +1098,108 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131038701</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131038703</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Karlslund, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>454998</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6515703</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Töreboda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älgarås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Sjövall</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131038703</t>
         </is>
@@ -1092,6 +1211,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
